--- a/output/details/2026-05-06/preprocessed_data.xlsx
+++ b/output/details/2026-05-06/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46148</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1079781370947511</v>
+        <v>-0.1075103753505631</v>
       </c>
       <c r="C2" t="n">
-        <v>0.20411500591135</v>
+        <v>-0.1321931529466478</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2038196173721161</v>
+        <v>-0.1319301147968294</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1339405062395656</v>
+        <v>0.01600335053652347</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703793849392244</v>
+        <v>0.001704159666054238</v>
       </c>
       <c r="G2" t="n">
-        <v>1.771032542309429</v>
+        <v>2.354592047010838</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4634137900842496</v>
+        <v>-0.256532232711926</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
